--- a/src/assets/samples/Import Add Device Template.xlsx
+++ b/src/assets/samples/Import Add Device Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afaqy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAB5017-D4A2-4478-A325-F458C8C654EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265452C5-500D-48A1-82E3-B9070B484EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8880" xr2:uid="{015474F9-D703-42F3-9422-1E6E79467DF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{015474F9-D703-42F3-9422-1E6E79467DF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ModelType</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Condition</t>
   </si>
   <si>
-    <t>ErrandChannel</t>
-  </si>
-  <si>
     <t>ShipmentId</t>
   </si>
   <si>
@@ -49,6 +46,18 @@
   </si>
   <si>
     <t>SIMSerial</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
@@ -118,9 +127,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -158,7 +167,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -264,7 +273,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,7 +415,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -414,13 +423,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F6681F3-CF7B-43CB-9BA1-2B4E8EA08F1B}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -428,25 +447,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -455,8 +483,10 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -465,8 +495,10 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -475,8 +507,10 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -485,8 +519,10 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -495,8 +531,10 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -505,8 +543,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -515,8 +555,10 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -525,8 +567,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -535,8 +579,10 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -545,8 +591,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -555,8 +603,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -565,6 +615,8 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
